--- a/data/trans_bre/P16A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,67</t>
+          <t>0,84; 3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,65</t>
+          <t>-0,51; 1,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,33</t>
+          <t>-0,01; 3,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,77; —</t>
+          <t>13,55; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 902,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,73; —</t>
+          <t>-66,74; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,24</t>
+          <t>-1,5; 1,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,02</t>
+          <t>-1,7; 2,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,42</t>
+          <t>-0,99; 2,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,21</t>
+          <t>-1,54; 2,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 112,72</t>
+          <t>-64,55; 115,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,31; 152,81</t>
+          <t>-54,13; 157,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 241,05</t>
+          <t>-42,5; 191,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,07; 399,03</t>
+          <t>-75,19; 382,01</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,42</t>
+          <t>0,97; 4,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,25</t>
+          <t>0,33; 4,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,78</t>
+          <t>0,51; 4,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,69</t>
+          <t>-0,45; 4,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,46; 625,34</t>
+          <t>34,48; 580,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 263,24</t>
+          <t>0,86; 242,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,66; 243,71</t>
+          <t>10,36; 248,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 172,35</t>
+          <t>-13,69; 196,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,49</t>
+          <t>1,36; 6,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,53</t>
+          <t>1,74; 7,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,38</t>
+          <t>1,18; 6,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 8,29</t>
+          <t>0,14; 7,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,38; 336,45</t>
+          <t>28,07; 339,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,96; 244,88</t>
+          <t>28,0; 250,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,17; 211,01</t>
+          <t>18,66; 217,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 319,56</t>
+          <t>1,27; 315,35</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,79</t>
+          <t>0,12; 7,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 11,01</t>
+          <t>4,09; 10,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,21</t>
+          <t>2,78; 10,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 9,58</t>
+          <t>3,85; 9,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 241,48</t>
+          <t>-5,8; 222,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,43; 519,17</t>
+          <t>76,62; 486,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,4; 249,54</t>
+          <t>28,26; 225,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,9; 216,42</t>
+          <t>53,79; 224,05</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,21; 10,53</t>
+          <t>1,51; 9,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 9,95</t>
+          <t>1,47; 9,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 12,49</t>
+          <t>4,52; 12,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 9,35</t>
+          <t>-2,29; 9,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,28; 328,28</t>
+          <t>17,19; 286,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 302,64</t>
+          <t>13,35; 299,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69,62; 524,94</t>
+          <t>70,34; 513,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 201,32</t>
+          <t>-33,31; 216,89</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 5,7</t>
+          <t>-3,66; 5,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,37</t>
+          <t>0,1; 10,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 11,12</t>
+          <t>1,5; 10,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 11,79</t>
+          <t>4,55; 12,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 126,34</t>
+          <t>-37,76; 129,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 205,67</t>
+          <t>-0,0; 214,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,84; 267,91</t>
+          <t>11,44; 260,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,4; 187,16</t>
+          <t>41,86; 199,19</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,67</t>
+          <t>1,74; 3,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,76</t>
+          <t>2,59; 4,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,35</t>
+          <t>3,09; 5,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,17</t>
+          <t>2,32; 5,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,93; 164,74</t>
+          <t>58,49; 167,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,66; 167,26</t>
+          <t>67,08; 171,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,32; 173,45</t>
+          <t>76,87; 174,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>54,4; 155,71</t>
+          <t>52,4; 157,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,7</t>
+          <t>0,68; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,67</t>
+          <t>-0,59; 1,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,49</t>
+          <t>-0,1; 3,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,55; —</t>
+          <t>24,14; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-66,74; —</t>
+          <t>-57,59; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,3</t>
+          <t>-1,47; 1,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,14</t>
+          <t>-1,73; 1,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,33</t>
+          <t>-1,01; 2,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,2</t>
+          <t>-1,42; 2,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 115,09</t>
+          <t>-63,69; 113,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 157,46</t>
+          <t>-56,37; 121,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,5; 191,13</t>
+          <t>-39,66; 195,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,19; 382,01</t>
+          <t>-59,71; 361,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,36</t>
+          <t>1,05; 4,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,98</t>
+          <t>0,31; 4,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,76</t>
+          <t>0,49; 4,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,08</t>
+          <t>-0,47; 3,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,48; 580,66</t>
+          <t>33,65; 663,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 242,95</t>
+          <t>2,24; 248,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 248,84</t>
+          <t>8,66; 233,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 196,6</t>
+          <t>-12,31; 187,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,72</t>
+          <t>1,31; 6,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,33</t>
+          <t>1,55; 7,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,37</t>
+          <t>0,96; 6,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 7,48</t>
+          <t>-1,22; 4,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,07; 339,36</t>
+          <t>26,3; 327,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,0; 250,12</t>
+          <t>27,88; 265,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 217,41</t>
+          <t>16,23; 210,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 315,35</t>
+          <t>-16,39; 83,76</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>114,2%</t>
+          <t>112,97%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 7,08</t>
+          <t>0,33; 7,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,88</t>
+          <t>3,94; 10,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,59</t>
+          <t>2,66; 10,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,43</t>
+          <t>3,71; 9,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 222,17</t>
+          <t>4,3; 256,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,62; 486,24</t>
+          <t>80,9; 497,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,26; 225,42</t>
+          <t>25,73; 230,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,79; 224,05</t>
+          <t>53,42; 199,87</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>9,01</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>182,81%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,84</t>
+          <t>1,73; 9,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 9,65</t>
+          <t>1,01; 9,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,68</t>
+          <t>4,46; 12,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 9,71</t>
+          <t>6,25; 12,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 286,35</t>
+          <t>19,99; 316,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,35; 299,71</t>
+          <t>8,27; 294,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,34; 513,55</t>
+          <t>73,91; 503,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 216,89</t>
+          <t>92,63; 343,73</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,56</t>
+          <t>8,95</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>104,7%</t>
+          <t>110,74%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 5,56</t>
+          <t>-3,39; 5,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 10,57</t>
+          <t>-0,12; 10,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 10,97</t>
+          <t>1,76; 10,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,2</t>
+          <t>5,3; 12,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-37,76; 129,25</t>
+          <t>-39,45; 120,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 214,3</t>
+          <t>-2,49; 214,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,44; 260,37</t>
+          <t>22,93; 250,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,86; 199,19</t>
+          <t>50,14; 214,22</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,64</t>
+          <t>1,76; 3,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,86</t>
+          <t>2,68; 4,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,34</t>
+          <t>3,05; 5,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,26</t>
+          <t>3,11; 5,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,49; 167,3</t>
+          <t>58,07; 164,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,08; 171,7</t>
+          <t>67,04; 166,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,87; 174,9</t>
+          <t>77,07; 173,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>52,4; 157,61</t>
+          <t>65,43; 137,06</t>
         </is>
       </c>
     </row>
